--- a/Data/aqualog_fdom/SampleDataSheet.xlsx
+++ b/Data/aqualog_fdom/SampleDataSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Donahue Lab\Desktop\GitHub\biofac\Data\aqualog_fdom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A61E829-3C37-4A8A-9B4B-25EABA4A4B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78CD19B1-BFF5-4BC0-AC0F-48A23A31BEE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14025" yWindow="-21600" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Run1" sheetId="4" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="130">
   <si>
     <t>SampleNumber</t>
   </si>
@@ -31,6 +31,387 @@
   </si>
   <si>
     <t>Notes</t>
+  </si>
+  <si>
+    <t>BLANK1</t>
+  </si>
+  <si>
+    <t>BIOFAC_1</t>
+  </si>
+  <si>
+    <t>BIOFAC_2</t>
+  </si>
+  <si>
+    <t>BIOFAC_3</t>
+  </si>
+  <si>
+    <t>BIOFAC_4</t>
+  </si>
+  <si>
+    <t>BIOFAC_5</t>
+  </si>
+  <si>
+    <t>BIOFAC_6</t>
+  </si>
+  <si>
+    <t>BIOFAC_7</t>
+  </si>
+  <si>
+    <t>BIOFAC_8</t>
+  </si>
+  <si>
+    <t>BIOFAC_9</t>
+  </si>
+  <si>
+    <t>BIOFAC_10</t>
+  </si>
+  <si>
+    <t>BLANK2</t>
+  </si>
+  <si>
+    <t>BIOFAC_11</t>
+  </si>
+  <si>
+    <t>BIOFAC_12</t>
+  </si>
+  <si>
+    <t>BIOFAC_13</t>
+  </si>
+  <si>
+    <t>BIOFAC_14</t>
+  </si>
+  <si>
+    <t>BIOFAC_15</t>
+  </si>
+  <si>
+    <t>BIOFAC_16</t>
+  </si>
+  <si>
+    <t>BIOFAC_17</t>
+  </si>
+  <si>
+    <t>BIOFAC_18</t>
+  </si>
+  <si>
+    <t>BIOFAC_19</t>
+  </si>
+  <si>
+    <t>BIOFAC_20</t>
+  </si>
+  <si>
+    <t>BLANK3</t>
+  </si>
+  <si>
+    <t>BIOFAC_21</t>
+  </si>
+  <si>
+    <t>BIOFAC_22</t>
+  </si>
+  <si>
+    <t>BIOFAC_23</t>
+  </si>
+  <si>
+    <t>BIOFAC_24</t>
+  </si>
+  <si>
+    <t>BIOFAC_25</t>
+  </si>
+  <si>
+    <t>BIOFAC_26</t>
+  </si>
+  <si>
+    <t>BIOFAC_27</t>
+  </si>
+  <si>
+    <t>BIOFAC_28</t>
+  </si>
+  <si>
+    <t>BIOFAC_29</t>
+  </si>
+  <si>
+    <t>BIOFAC_30</t>
+  </si>
+  <si>
+    <t>BIOFAC_31</t>
+  </si>
+  <si>
+    <t>BIOFAC_32</t>
+  </si>
+  <si>
+    <t>BIOFAC_33</t>
+  </si>
+  <si>
+    <t>BIOFAC_34</t>
+  </si>
+  <si>
+    <t>BIOFAC_35</t>
+  </si>
+  <si>
+    <t>BIOFAC_36</t>
+  </si>
+  <si>
+    <t>BIOFAC_37</t>
+  </si>
+  <si>
+    <t>BIOFAC_38</t>
+  </si>
+  <si>
+    <t>BIOFAC_39</t>
+  </si>
+  <si>
+    <t>BIOFAC_40</t>
+  </si>
+  <si>
+    <t>BIOFAC_41</t>
+  </si>
+  <si>
+    <t>BIOFAC_42</t>
+  </si>
+  <si>
+    <t>BIOFAC_43</t>
+  </si>
+  <si>
+    <t>BIOFAC_44</t>
+  </si>
+  <si>
+    <t>BIOFAC_45</t>
+  </si>
+  <si>
+    <t>BIOFAC_46</t>
+  </si>
+  <si>
+    <t>BIOFAC_47</t>
+  </si>
+  <si>
+    <t>BIOFAC_48</t>
+  </si>
+  <si>
+    <t>BIOFAC_49</t>
+  </si>
+  <si>
+    <t>BIOFAC_50</t>
+  </si>
+  <si>
+    <t>BIOFAC_51</t>
+  </si>
+  <si>
+    <t>BIOFAC_52</t>
+  </si>
+  <si>
+    <t>BIOFAC_53</t>
+  </si>
+  <si>
+    <t>BIOFAC_54</t>
+  </si>
+  <si>
+    <t>BIOFAC_55</t>
+  </si>
+  <si>
+    <t>BIOFAC_56</t>
+  </si>
+  <si>
+    <t>BIOFAC_57</t>
+  </si>
+  <si>
+    <t>BIOFAC_58</t>
+  </si>
+  <si>
+    <t>BIOFAC_59</t>
+  </si>
+  <si>
+    <t>BIOFAC_60</t>
+  </si>
+  <si>
+    <t>BIOFAC_61</t>
+  </si>
+  <si>
+    <t>BIOFAC_62</t>
+  </si>
+  <si>
+    <t>BIOFAC_63</t>
+  </si>
+  <si>
+    <t>BIOFAC_64</t>
+  </si>
+  <si>
+    <t>BIOFAC_65</t>
+  </si>
+  <si>
+    <t>BIOFAC_66</t>
+  </si>
+  <si>
+    <t>BIOFAC_67</t>
+  </si>
+  <si>
+    <t>BIOFAC_68</t>
+  </si>
+  <si>
+    <t>BIOFAC_69</t>
+  </si>
+  <si>
+    <t>BIOFAC_70</t>
+  </si>
+  <si>
+    <t>BIOFAC_71</t>
+  </si>
+  <si>
+    <t>BIOFAC_72</t>
+  </si>
+  <si>
+    <t>BIOFAC_73</t>
+  </si>
+  <si>
+    <t>BIOFAC_74</t>
+  </si>
+  <si>
+    <t>BIOFAC_75</t>
+  </si>
+  <si>
+    <t>BIOFAC_76</t>
+  </si>
+  <si>
+    <t>BIOFAC_77</t>
+  </si>
+  <si>
+    <t>BIOFAC_78</t>
+  </si>
+  <si>
+    <t>BIOFAC_79</t>
+  </si>
+  <si>
+    <t>BIOFAC_80</t>
+  </si>
+  <si>
+    <t>BIOFAC_81</t>
+  </si>
+  <si>
+    <t>BIOFAC_82</t>
+  </si>
+  <si>
+    <t>BIOFAC_83</t>
+  </si>
+  <si>
+    <t>BLANK4</t>
+  </si>
+  <si>
+    <t>BIOFAC_84</t>
+  </si>
+  <si>
+    <t>BIOFAC_85</t>
+  </si>
+  <si>
+    <t>BIOFAC_86</t>
+  </si>
+  <si>
+    <t>BIOFAC_87</t>
+  </si>
+  <si>
+    <t>BIOFAC_88</t>
+  </si>
+  <si>
+    <t>BIOFAC_89</t>
+  </si>
+  <si>
+    <t>BIOFAC_90</t>
+  </si>
+  <si>
+    <t>BIOFAC_91</t>
+  </si>
+  <si>
+    <t>BIOFAC_92</t>
+  </si>
+  <si>
+    <t>BIOFAC_93</t>
+  </si>
+  <si>
+    <t>BLANK5</t>
+  </si>
+  <si>
+    <t>BIOFAC_94</t>
+  </si>
+  <si>
+    <t>BIOFAC_95</t>
+  </si>
+  <si>
+    <t>BIOFAC_96</t>
+  </si>
+  <si>
+    <t>BIOFAC_97</t>
+  </si>
+  <si>
+    <t>BIOFAC_98</t>
+  </si>
+  <si>
+    <t>BIOFAC_99</t>
+  </si>
+  <si>
+    <t>BIOFAC_100</t>
+  </si>
+  <si>
+    <t>BIOFAC_101</t>
+  </si>
+  <si>
+    <t>BIOFAC_102</t>
+  </si>
+  <si>
+    <t>BIOFAC_103</t>
+  </si>
+  <si>
+    <t>BLANK6</t>
+  </si>
+  <si>
+    <t>BIOFAC_104</t>
+  </si>
+  <si>
+    <t>BIOFAC_105</t>
+  </si>
+  <si>
+    <t>BIOFAC_106</t>
+  </si>
+  <si>
+    <t>BIOFAC_107</t>
+  </si>
+  <si>
+    <t>BIOFAC_108</t>
+  </si>
+  <si>
+    <t>BIOFAC_109</t>
+  </si>
+  <si>
+    <t>BIOFAC_110</t>
+  </si>
+  <si>
+    <t>BIOFAC_111</t>
+  </si>
+  <si>
+    <t>BIOFAC_112</t>
+  </si>
+  <si>
+    <t>BIOFAC_113</t>
+  </si>
+  <si>
+    <t>BLANK7</t>
+  </si>
+  <si>
+    <t>BIOFAC_114</t>
+  </si>
+  <si>
+    <t>BIOFAC_115</t>
+  </si>
+  <si>
+    <t>BIOFAC_116</t>
+  </si>
+  <si>
+    <t>BIOFAC_117</t>
+  </si>
+  <si>
+    <t>BIOFAC_118</t>
+  </si>
+  <si>
+    <t>BIOFAC_119</t>
+  </si>
+  <si>
+    <t>BIOFAC_120</t>
   </si>
 </sst>
 </file>
@@ -286,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CB9875A-A731-487F-A74D-27E5BA5E3865}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -298,6 +679,270 @@
       </c>
       <c r="C1" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -307,7 +952,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7984AFD9-7A75-40DA-A3D5-69022F0C5A2B}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -319,6 +964,214 @@
       </c>
       <c r="C1" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -328,8 +1181,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3858D8CA-F221-4E96-8F87-B1EA99B50EF2}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C75"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -342,6 +1199,598 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/aqualog_fdom/SampleDataSheet.xlsx
+++ b/Data/aqualog_fdom/SampleDataSheet.xlsx
@@ -1,28 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Donahue Lab\Desktop\GitHub\biofac\Data\aqualog_fdom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78CD19B1-BFF5-4BC0-AC0F-48A23A31BEE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E05243-BCE5-4D2B-A50F-932A4DB5DDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14025" yWindow="-21600" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Run1" sheetId="4" r:id="rId1"/>
     <sheet name="Run2" sheetId="5" r:id="rId2"/>
     <sheet name="Run3" sheetId="3" r:id="rId3"/>
+    <sheet name="Run4" sheetId="6" r:id="rId4"/>
+    <sheet name="Run5" sheetId="7" r:id="rId5"/>
+    <sheet name="Blankrun" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="249">
   <si>
     <t>SampleNumber</t>
   </si>
@@ -412,6 +415,363 @@
   </si>
   <si>
     <t>BIOFAC_120</t>
+  </si>
+  <si>
+    <t>BIOFAC_121</t>
+  </si>
+  <si>
+    <t>BIOFAC_122</t>
+  </si>
+  <si>
+    <t>BIOFAC_123</t>
+  </si>
+  <si>
+    <t>BIOFAC_124</t>
+  </si>
+  <si>
+    <t>BIOFAC_125</t>
+  </si>
+  <si>
+    <t>BIOFAC_126</t>
+  </si>
+  <si>
+    <t>BIOFAC_127</t>
+  </si>
+  <si>
+    <t>BIOFAC_128</t>
+  </si>
+  <si>
+    <t>BIOFAC_129</t>
+  </si>
+  <si>
+    <t>BIOFAC_130</t>
+  </si>
+  <si>
+    <t>BIOFAC_131</t>
+  </si>
+  <si>
+    <t>BIOFAC_132</t>
+  </si>
+  <si>
+    <t>BIOFAC_133</t>
+  </si>
+  <si>
+    <t>BIOFAC_134</t>
+  </si>
+  <si>
+    <t>BIOFAC_135</t>
+  </si>
+  <si>
+    <t>BIOFAC_136</t>
+  </si>
+  <si>
+    <t>BIOFAC_137</t>
+  </si>
+  <si>
+    <t>BIOFAC_138</t>
+  </si>
+  <si>
+    <t>BIOFAC_139</t>
+  </si>
+  <si>
+    <t>BIOFAC_140</t>
+  </si>
+  <si>
+    <t>BIOFAC_141</t>
+  </si>
+  <si>
+    <t>BIOFAC_142</t>
+  </si>
+  <si>
+    <t>BIOFAC_143</t>
+  </si>
+  <si>
+    <t>BIOFAC_144</t>
+  </si>
+  <si>
+    <t>BIOFAC_145</t>
+  </si>
+  <si>
+    <t>BIOFAC_146</t>
+  </si>
+  <si>
+    <t>BIOFAC_147</t>
+  </si>
+  <si>
+    <t>BIOFAC_148</t>
+  </si>
+  <si>
+    <t>BIOFAC_149</t>
+  </si>
+  <si>
+    <t>BIOFAC_150</t>
+  </si>
+  <si>
+    <t>BIOFAC_151</t>
+  </si>
+  <si>
+    <t>BIOFAC_152</t>
+  </si>
+  <si>
+    <t>BIOFAC_153</t>
+  </si>
+  <si>
+    <t>BIOFAC_154</t>
+  </si>
+  <si>
+    <t>BIOFAC_155</t>
+  </si>
+  <si>
+    <t>BIOFAC_156</t>
+  </si>
+  <si>
+    <t>BIOFAC_157</t>
+  </si>
+  <si>
+    <t>BIOFAC_158</t>
+  </si>
+  <si>
+    <t>BIOFAC_159</t>
+  </si>
+  <si>
+    <t>BIOFAC_160</t>
+  </si>
+  <si>
+    <t>BIOFAC_161</t>
+  </si>
+  <si>
+    <t>BIOFAC_162</t>
+  </si>
+  <si>
+    <t>BIOFAC_163</t>
+  </si>
+  <si>
+    <t>BIOFAC_164</t>
+  </si>
+  <si>
+    <t>BIOFAC_165</t>
+  </si>
+  <si>
+    <t>BIOFAC_166</t>
+  </si>
+  <si>
+    <t>BIOFAC_167</t>
+  </si>
+  <si>
+    <t>BIOFAC_168</t>
+  </si>
+  <si>
+    <t>BIOFAC_169</t>
+  </si>
+  <si>
+    <t>BIOFAC_170</t>
+  </si>
+  <si>
+    <t>BIOFAC_171</t>
+  </si>
+  <si>
+    <t>BIOFAC_172</t>
+  </si>
+  <si>
+    <t>BIOFAC_173</t>
+  </si>
+  <si>
+    <t>BIOFAC_174</t>
+  </si>
+  <si>
+    <t>BIOFAC_175</t>
+  </si>
+  <si>
+    <t>BIOFAC_176</t>
+  </si>
+  <si>
+    <t>BIOFAC_177</t>
+  </si>
+  <si>
+    <t>BIOFAC_178</t>
+  </si>
+  <si>
+    <t>BIOFAC_179</t>
+  </si>
+  <si>
+    <t>BIOFAC_180</t>
+  </si>
+  <si>
+    <t>BIOFAC_181</t>
+  </si>
+  <si>
+    <t>BIOFAC_182</t>
+  </si>
+  <si>
+    <t>BIOFAC_183</t>
+  </si>
+  <si>
+    <t>BIOFAC_184</t>
+  </si>
+  <si>
+    <t>BIOFAC_185</t>
+  </si>
+  <si>
+    <t>BIOFAC_186</t>
+  </si>
+  <si>
+    <t>BIOFAC_187</t>
+  </si>
+  <si>
+    <t>BIOFAC_188</t>
+  </si>
+  <si>
+    <t>BIOFAC_189</t>
+  </si>
+  <si>
+    <t>BIOFAC_190</t>
+  </si>
+  <si>
+    <t>BIOFAC_191</t>
+  </si>
+  <si>
+    <t>BIOFAC_192</t>
+  </si>
+  <si>
+    <t>BIOFAC_193</t>
+  </si>
+  <si>
+    <t>BIOFAC_194</t>
+  </si>
+  <si>
+    <t>BIOFAC_195</t>
+  </si>
+  <si>
+    <t>BIOFAC_196</t>
+  </si>
+  <si>
+    <t>BIOFAC_197</t>
+  </si>
+  <si>
+    <t>BIOFAC_198</t>
+  </si>
+  <si>
+    <t>BIOFAC_199</t>
+  </si>
+  <si>
+    <t>BIOFAC_200</t>
+  </si>
+  <si>
+    <t>BIOFAC_201</t>
+  </si>
+  <si>
+    <t>BIOFAC_202</t>
+  </si>
+  <si>
+    <t>BIOFAC_203</t>
+  </si>
+  <si>
+    <t>BIOFAC_204</t>
+  </si>
+  <si>
+    <t>BIOFAC_205</t>
+  </si>
+  <si>
+    <t>BIOFAC_206</t>
+  </si>
+  <si>
+    <t>BIOFAC_207</t>
+  </si>
+  <si>
+    <t>BIOFAC_208</t>
+  </si>
+  <si>
+    <t>BIOFAC_209</t>
+  </si>
+  <si>
+    <t>BIOFAC_210</t>
+  </si>
+  <si>
+    <t>BIOFAC_211</t>
+  </si>
+  <si>
+    <t>BIOFAC_212</t>
+  </si>
+  <si>
+    <t>BIOFAC_213</t>
+  </si>
+  <si>
+    <t>BIOFAC_214</t>
+  </si>
+  <si>
+    <t>BIOFAC_215</t>
+  </si>
+  <si>
+    <t>BIOFAC_216</t>
+  </si>
+  <si>
+    <t>BIOFAC_217</t>
+  </si>
+  <si>
+    <t>BIOFAC_218</t>
+  </si>
+  <si>
+    <t>BIOFAC_219</t>
+  </si>
+  <si>
+    <t>BIOFAC_220</t>
+  </si>
+  <si>
+    <t>BIOFAC_221</t>
+  </si>
+  <si>
+    <t>BIOFAC_222</t>
+  </si>
+  <si>
+    <t>BIOFAC_223</t>
+  </si>
+  <si>
+    <t>BIOFAC_224</t>
+  </si>
+  <si>
+    <t>BIOFAC_225</t>
+  </si>
+  <si>
+    <t>BIOFAC_226</t>
+  </si>
+  <si>
+    <t>BIOFAC_227</t>
+  </si>
+  <si>
+    <t>BIOFAC_228</t>
+  </si>
+  <si>
+    <t>BIOFAC_229</t>
+  </si>
+  <si>
+    <t>BIOFAC_230</t>
+  </si>
+  <si>
+    <t>BIOFAC_231</t>
+  </si>
+  <si>
+    <t>BIOFAC_232</t>
+  </si>
+  <si>
+    <t>BIOFAC_233</t>
+  </si>
+  <si>
+    <t>BIOFAC_234</t>
+  </si>
+  <si>
+    <t>BIOFAC_235</t>
+  </si>
+  <si>
+    <t>BIOFAC_236</t>
+  </si>
+  <si>
+    <t>BIOFAC_237</t>
+  </si>
+  <si>
+    <t>BIOFAC_238</t>
+  </si>
+  <si>
+    <t>BIOFAC_239</t>
   </si>
 </sst>
 </file>
@@ -463,10 +823,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1794,4 +2150,1454 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB8D2A89-8AFA-4CBF-BD91-0A803B7E23BF}">
+  <dimension ref="A1:B67"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>189</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3798B9AB-AD36-442D-8BCD-F96228A64225}">
+  <dimension ref="A1:B66"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>248</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DF34553-FC16-4C39-B9D7-D6998E16C3C1}">
+  <dimension ref="A1:B67"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Data/aqualog_fdom/SampleDataSheet.xlsx
+++ b/Data/aqualog_fdom/SampleDataSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Donahue Lab\Desktop\GitHub\biofac\Data\aqualog_fdom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E05243-BCE5-4D2B-A50F-932A4DB5DDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6860A41C-0C60-4D8D-9823-6E9A62353EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Run1" sheetId="4" r:id="rId1"/>
@@ -18,14 +18,17 @@
     <sheet name="Run3" sheetId="3" r:id="rId3"/>
     <sheet name="Run4" sheetId="6" r:id="rId4"/>
     <sheet name="Run5" sheetId="7" r:id="rId5"/>
-    <sheet name="Blankrun" sheetId="8" r:id="rId6"/>
+    <sheet name="Run6" sheetId="9" r:id="rId6"/>
+    <sheet name="Run7" sheetId="10" r:id="rId7"/>
+    <sheet name="Run8" sheetId="11" r:id="rId8"/>
+    <sheet name="Blankrun" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="428">
   <si>
     <t>SampleNumber</t>
   </si>
@@ -772,16 +775,558 @@
   </si>
   <si>
     <t>BIOFAC_239</t>
+  </si>
+  <si>
+    <t>BIOFAC_240</t>
+  </si>
+  <si>
+    <t>BIOFAC_241</t>
+  </si>
+  <si>
+    <t>BIOFAC_242</t>
+  </si>
+  <si>
+    <t>BIOFAC_243</t>
+  </si>
+  <si>
+    <t>BIOFAC_244</t>
+  </si>
+  <si>
+    <t>BIOFAC_245</t>
+  </si>
+  <si>
+    <t>BIOFAC_246</t>
+  </si>
+  <si>
+    <t>BIOFAC_247</t>
+  </si>
+  <si>
+    <t>BIOFAC_248</t>
+  </si>
+  <si>
+    <t>BIOFAC_249</t>
+  </si>
+  <si>
+    <t>BIOFAC_250</t>
+  </si>
+  <si>
+    <t>BIOFAC_251</t>
+  </si>
+  <si>
+    <t>BIOFAC_252</t>
+  </si>
+  <si>
+    <t>BIOFAC_253</t>
+  </si>
+  <si>
+    <t>BIOFAC_254</t>
+  </si>
+  <si>
+    <t>BIOFAC_255</t>
+  </si>
+  <si>
+    <t>BIOFAC_256</t>
+  </si>
+  <si>
+    <t>BIOFAC_257</t>
+  </si>
+  <si>
+    <t>BIOFAC_258</t>
+  </si>
+  <si>
+    <t>BIOFAC_259</t>
+  </si>
+  <si>
+    <t>BIOFAC_260</t>
+  </si>
+  <si>
+    <t>BIOFAC_261</t>
+  </si>
+  <si>
+    <t>BIOFAC_262</t>
+  </si>
+  <si>
+    <t>BIOFAC_263</t>
+  </si>
+  <si>
+    <t>BIOFAC_264</t>
+  </si>
+  <si>
+    <t>BIOFAC_265</t>
+  </si>
+  <si>
+    <t>BIOFAC_266</t>
+  </si>
+  <si>
+    <t>BIOFAC_267</t>
+  </si>
+  <si>
+    <t>BIOFAC_268</t>
+  </si>
+  <si>
+    <t>BIOFAC_269</t>
+  </si>
+  <si>
+    <t>BIOFAC_270</t>
+  </si>
+  <si>
+    <t>BIOFAC_271</t>
+  </si>
+  <si>
+    <t>BIOFAC_272</t>
+  </si>
+  <si>
+    <t>BIOFAC_273</t>
+  </si>
+  <si>
+    <t>BIOFAC_274</t>
+  </si>
+  <si>
+    <t>BIOFAC_275</t>
+  </si>
+  <si>
+    <t>BIOFAC_276</t>
+  </si>
+  <si>
+    <t>BIOFAC_277</t>
+  </si>
+  <si>
+    <t>BIOFAC_278</t>
+  </si>
+  <si>
+    <t>BIOFAC_279</t>
+  </si>
+  <si>
+    <t>BIOFAC_280</t>
+  </si>
+  <si>
+    <t>BIOFAC_281</t>
+  </si>
+  <si>
+    <t>BIOFAC_282</t>
+  </si>
+  <si>
+    <t>BIOFAC_283</t>
+  </si>
+  <si>
+    <t>BIOFAC_284</t>
+  </si>
+  <si>
+    <t>BIOFAC_285</t>
+  </si>
+  <si>
+    <t>BIOFAC_286</t>
+  </si>
+  <si>
+    <t>BIOFAC_287</t>
+  </si>
+  <si>
+    <t>BIOFAC_288</t>
+  </si>
+  <si>
+    <t>BIOFAC_289</t>
+  </si>
+  <si>
+    <t>BIOFAC_290</t>
+  </si>
+  <si>
+    <t>BIOFAC_291</t>
+  </si>
+  <si>
+    <t>BIOFAC_292</t>
+  </si>
+  <si>
+    <t>BIOFAC_293</t>
+  </si>
+  <si>
+    <t>BIOFAC_294</t>
+  </si>
+  <si>
+    <t>BIOFAC_295</t>
+  </si>
+  <si>
+    <t>BIOFAC_296</t>
+  </si>
+  <si>
+    <t>BIOFAC_297</t>
+  </si>
+  <si>
+    <t>BIOFAC_298</t>
+  </si>
+  <si>
+    <t>BIOFAC_299</t>
+  </si>
+  <si>
+    <t>BIOFAC_300</t>
+  </si>
+  <si>
+    <t>BIOFAC_301</t>
+  </si>
+  <si>
+    <t>BIOFAC_302</t>
+  </si>
+  <si>
+    <t>BIOFAC_303</t>
+  </si>
+  <si>
+    <t>BIOFAC_304</t>
+  </si>
+  <si>
+    <t>BIOFAC_305</t>
+  </si>
+  <si>
+    <t>BIOFAC_306</t>
+  </si>
+  <si>
+    <t>BIOFAC_307</t>
+  </si>
+  <si>
+    <t>BIOFAC_308</t>
+  </si>
+  <si>
+    <t>BIOFAC_309</t>
+  </si>
+  <si>
+    <t>BIOFAC_310</t>
+  </si>
+  <si>
+    <t>BIOFAC_311</t>
+  </si>
+  <si>
+    <t>BIOFAC_312</t>
+  </si>
+  <si>
+    <t>BIOFAC_313</t>
+  </si>
+  <si>
+    <t>BIOFAC_314</t>
+  </si>
+  <si>
+    <t>BIOFAC_315</t>
+  </si>
+  <si>
+    <t>BIOFAC_316</t>
+  </si>
+  <si>
+    <t>BIOFAC_317</t>
+  </si>
+  <si>
+    <t>BIOFAC_318</t>
+  </si>
+  <si>
+    <t>BIOFAC_319</t>
+  </si>
+  <si>
+    <t>BIOFAC_320</t>
+  </si>
+  <si>
+    <t>BIOFAC_321</t>
+  </si>
+  <si>
+    <t>BIOFAC_322</t>
+  </si>
+  <si>
+    <t>BIOFAC_323</t>
+  </si>
+  <si>
+    <t>BIOFAC_324</t>
+  </si>
+  <si>
+    <t>BIOFAC_325</t>
+  </si>
+  <si>
+    <t>BIOFAC_326</t>
+  </si>
+  <si>
+    <t>BIOFAC_327</t>
+  </si>
+  <si>
+    <t>BIOFAC_328</t>
+  </si>
+  <si>
+    <t>BIOFAC_329</t>
+  </si>
+  <si>
+    <t>BIOFAC_330</t>
+  </si>
+  <si>
+    <t>BIOFAC_331</t>
+  </si>
+  <si>
+    <t>BIOFAC_332</t>
+  </si>
+  <si>
+    <t>BIOFAC_333</t>
+  </si>
+  <si>
+    <t>BIOFAC_334</t>
+  </si>
+  <si>
+    <t>BIOFAC_335</t>
+  </si>
+  <si>
+    <t>BIOFAC_336</t>
+  </si>
+  <si>
+    <t>BIOFAC_348</t>
+  </si>
+  <si>
+    <t>BIOFAC_349</t>
+  </si>
+  <si>
+    <t>BIOFAC_350</t>
+  </si>
+  <si>
+    <t>BIOFAC_351</t>
+  </si>
+  <si>
+    <t>BIOFAC_352</t>
+  </si>
+  <si>
+    <t>BIOFAC_353</t>
+  </si>
+  <si>
+    <t>BIOFAC_354</t>
+  </si>
+  <si>
+    <t>BIOFAC_355</t>
+  </si>
+  <si>
+    <t>BIOFAC_356</t>
+  </si>
+  <si>
+    <t>BIOFAC_357</t>
+  </si>
+  <si>
+    <t>BIOFAC_358</t>
+  </si>
+  <si>
+    <t>BIOFAC_359</t>
+  </si>
+  <si>
+    <t>BIOFAC_360</t>
+  </si>
+  <si>
+    <t>BIOFAC_361</t>
+  </si>
+  <si>
+    <t>BIOFAC_362</t>
+  </si>
+  <si>
+    <t>BIOFAC_363</t>
+  </si>
+  <si>
+    <t>BIOFAC_364</t>
+  </si>
+  <si>
+    <t>BIOFAC_365</t>
+  </si>
+  <si>
+    <t>BIOFAC_366</t>
+  </si>
+  <si>
+    <t>BIOFAC_367</t>
+  </si>
+  <si>
+    <t>BIOFAC_368</t>
+  </si>
+  <si>
+    <t>BIOFAC_369</t>
+  </si>
+  <si>
+    <t>BIOFAC_370</t>
+  </si>
+  <si>
+    <t>BIOFAC_371</t>
+  </si>
+  <si>
+    <t>BIOFAC_372</t>
+  </si>
+  <si>
+    <t>BIOFAC_373</t>
+  </si>
+  <si>
+    <t>BIOFAC_374</t>
+  </si>
+  <si>
+    <t>BIOFAC_375</t>
+  </si>
+  <si>
+    <t>BIOFAC_376</t>
+  </si>
+  <si>
+    <t>BIOFAC_377</t>
+  </si>
+  <si>
+    <t>BIOFAC_378</t>
+  </si>
+  <si>
+    <t>BIOFAC_379</t>
+  </si>
+  <si>
+    <t>BIOFAC_380</t>
+  </si>
+  <si>
+    <t>BIOFAC_381</t>
+  </si>
+  <si>
+    <t>BIOFAC_382</t>
+  </si>
+  <si>
+    <t>BIOFAC_383</t>
+  </si>
+  <si>
+    <t>BIOFAC_384</t>
+  </si>
+  <si>
+    <t>BIOFAC_385</t>
+  </si>
+  <si>
+    <t>BIOFAC_386</t>
+  </si>
+  <si>
+    <t>BIOFAC_387</t>
+  </si>
+  <si>
+    <t>BIOFAC_388</t>
+  </si>
+  <si>
+    <t>BIOFAC_389</t>
+  </si>
+  <si>
+    <t>BIOFAC_390</t>
+  </si>
+  <si>
+    <t>BIOFAC_391</t>
+  </si>
+  <si>
+    <t>BIOFAC_392</t>
+  </si>
+  <si>
+    <t>BIOFAC_393</t>
+  </si>
+  <si>
+    <t>BIOFAC_394</t>
+  </si>
+  <si>
+    <t>BIOFAC_395</t>
+  </si>
+  <si>
+    <t>BIOFAC_396</t>
+  </si>
+  <si>
+    <t>BIOFAC_397</t>
+  </si>
+  <si>
+    <t>BIOFAC_398</t>
+  </si>
+  <si>
+    <t>BIOFAC_399</t>
+  </si>
+  <si>
+    <t>BIOFAC_400</t>
+  </si>
+  <si>
+    <t>BIOFAC_401</t>
+  </si>
+  <si>
+    <t>BIOFAC_402</t>
+  </si>
+  <si>
+    <t>BIOFAC_403</t>
+  </si>
+  <si>
+    <t>BIOFAC_404</t>
+  </si>
+  <si>
+    <t>BIOFAC_405</t>
+  </si>
+  <si>
+    <t>BIOFAC_406</t>
+  </si>
+  <si>
+    <t>BIOFAC_407</t>
+  </si>
+  <si>
+    <t>BIOFAC_408</t>
+  </si>
+  <si>
+    <t>BIOFAC_409</t>
+  </si>
+  <si>
+    <t>BIOFAC_410</t>
+  </si>
+  <si>
+    <t>BIOFAC_411</t>
+  </si>
+  <si>
+    <t>BIOFAC_412</t>
+  </si>
+  <si>
+    <t>BIOFAC_413</t>
+  </si>
+  <si>
+    <t>BIOFAC_414</t>
+  </si>
+  <si>
+    <t>BIOFAC_415</t>
+  </si>
+  <si>
+    <t>BIOFAC_416</t>
+  </si>
+  <si>
+    <t>BIOFAC_417</t>
+  </si>
+  <si>
+    <t>BIOFAC_337</t>
+  </si>
+  <si>
+    <t>BIOFAC_338</t>
+  </si>
+  <si>
+    <t>BIOFAC_339</t>
+  </si>
+  <si>
+    <t>BLANK8</t>
+  </si>
+  <si>
+    <t>BIOFAC_340</t>
+  </si>
+  <si>
+    <t>BIOFAC_341</t>
+  </si>
+  <si>
+    <t>BIOFAC_342</t>
+  </si>
+  <si>
+    <t>BIOFAC_343</t>
+  </si>
+  <si>
+    <t>BIOFAC_344</t>
+  </si>
+  <si>
+    <t>BIOFAC_345</t>
+  </si>
+  <si>
+    <t>BIOFAC_346</t>
+  </si>
+  <si>
+    <t>BIOFAC_347</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -3237,6 +3782,1629 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C2C963C-070C-453A-ABDC-FCBD98D39D11}">
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>278</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B8F7C16-219F-42CB-8E83-F80250BF1C16}">
+  <dimension ref="A1:B87"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>427</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24F5383B-293F-4DB5-A388-B65AD9E8A28C}">
+  <dimension ref="A1:B78"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>415</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DF34553-FC16-4C39-B9D7-D6998E16C3C1}">
   <dimension ref="A1:B67"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>

--- a/Data/aqualog_fdom/SampleDataSheet.xlsx
+++ b/Data/aqualog_fdom/SampleDataSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Donahue Lab\Desktop\GitHub\biofac\Data\aqualog_fdom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6860A41C-0C60-4D8D-9823-6E9A62353EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8574C59-6581-41B3-A4AD-4406D8B2E942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Run1" sheetId="4" r:id="rId1"/>

--- a/Data/aqualog_fdom/SampleDataSheet.xlsx
+++ b/Data/aqualog_fdom/SampleDataSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Donahue Lab\Desktop\GitHub\biofac\Data\aqualog_fdom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8574C59-6581-41B3-A4AD-4406D8B2E942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7F9D81-B66E-4241-AF8C-60DD6CC1281B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Run1" sheetId="4" r:id="rId1"/>
@@ -21,14 +21,15 @@
     <sheet name="Run6" sheetId="9" r:id="rId6"/>
     <sheet name="Run7" sheetId="10" r:id="rId7"/>
     <sheet name="Run8" sheetId="11" r:id="rId8"/>
-    <sheet name="Blankrun" sheetId="8" r:id="rId9"/>
+    <sheet name="Run9" sheetId="12" r:id="rId9"/>
+    <sheet name="Run10" sheetId="8" r:id="rId10"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="579">
   <si>
     <t>SampleNumber</t>
   </si>
@@ -1312,6 +1313,459 @@
   </si>
   <si>
     <t>BIOFAC_347</t>
+  </si>
+  <si>
+    <t>BIOFAC_418</t>
+  </si>
+  <si>
+    <t>BIOFAC_419</t>
+  </si>
+  <si>
+    <t>BIOFAC_420</t>
+  </si>
+  <si>
+    <t>BIOFAC_421</t>
+  </si>
+  <si>
+    <t>BIOFAC_422</t>
+  </si>
+  <si>
+    <t>BIOFAC_423</t>
+  </si>
+  <si>
+    <t>BIOFAC_424</t>
+  </si>
+  <si>
+    <t>BIOFAC_425</t>
+  </si>
+  <si>
+    <t>BIOFAC_426</t>
+  </si>
+  <si>
+    <t>BIOFAC_427</t>
+  </si>
+  <si>
+    <t>BIOFAC_428</t>
+  </si>
+  <si>
+    <t>BIOFAC_429</t>
+  </si>
+  <si>
+    <t>BIOFAC_430</t>
+  </si>
+  <si>
+    <t>BIOFAC_431</t>
+  </si>
+  <si>
+    <t>BIOFAC_432</t>
+  </si>
+  <si>
+    <t>BIOFAC_433</t>
+  </si>
+  <si>
+    <t>BIOFAC_434</t>
+  </si>
+  <si>
+    <t>BIOFAC_435</t>
+  </si>
+  <si>
+    <t>BIOFAC_436</t>
+  </si>
+  <si>
+    <t>BIOFAC_437</t>
+  </si>
+  <si>
+    <t>BIOFAC_438</t>
+  </si>
+  <si>
+    <t>BIOFAC_439</t>
+  </si>
+  <si>
+    <t>BIOFAC_440</t>
+  </si>
+  <si>
+    <t>BIOFAC_441</t>
+  </si>
+  <si>
+    <t>BIOFAC_442</t>
+  </si>
+  <si>
+    <t>BIOFAC_443</t>
+  </si>
+  <si>
+    <t>BIOFAC_444</t>
+  </si>
+  <si>
+    <t>BIOFAC_445</t>
+  </si>
+  <si>
+    <t>BIOFAC_446</t>
+  </si>
+  <si>
+    <t>BIOFAC_447</t>
+  </si>
+  <si>
+    <t>BIOFAC_448</t>
+  </si>
+  <si>
+    <t>BIOFAC_449</t>
+  </si>
+  <si>
+    <t>BIOFAC_450</t>
+  </si>
+  <si>
+    <t>BIOFAC_451</t>
+  </si>
+  <si>
+    <t>BIOFAC_452</t>
+  </si>
+  <si>
+    <t>BIOFAC_453</t>
+  </si>
+  <si>
+    <t>BIOFAC_454</t>
+  </si>
+  <si>
+    <t>BIOFAC_455</t>
+  </si>
+  <si>
+    <t>BIOFAC_456</t>
+  </si>
+  <si>
+    <t>BIOFAC_457</t>
+  </si>
+  <si>
+    <t>BIOFAC_458</t>
+  </si>
+  <si>
+    <t>BIOFAC_459</t>
+  </si>
+  <si>
+    <t>BIOFAC_460</t>
+  </si>
+  <si>
+    <t>BIOFAC_461</t>
+  </si>
+  <si>
+    <t>BIOFAC_462</t>
+  </si>
+  <si>
+    <t>BIOFAC_463</t>
+  </si>
+  <si>
+    <t>BIOFAC_464</t>
+  </si>
+  <si>
+    <t>BIOFAC_465</t>
+  </si>
+  <si>
+    <t>BIOFAC_466</t>
+  </si>
+  <si>
+    <t>BIOFAC_467</t>
+  </si>
+  <si>
+    <t>BIOFAC_468</t>
+  </si>
+  <si>
+    <t>BIOFAC_469</t>
+  </si>
+  <si>
+    <t>BIOFAC_470</t>
+  </si>
+  <si>
+    <t>BIOFAC_471</t>
+  </si>
+  <si>
+    <t>BIOFAC_472</t>
+  </si>
+  <si>
+    <t>BIOFAC_473</t>
+  </si>
+  <si>
+    <t>BIOFAC_474</t>
+  </si>
+  <si>
+    <t>BIOFAC_475</t>
+  </si>
+  <si>
+    <t>BIOFAC_476</t>
+  </si>
+  <si>
+    <t>BIOFAC_477</t>
+  </si>
+  <si>
+    <t>BLANK9</t>
+  </si>
+  <si>
+    <t>BIOFAC_478</t>
+  </si>
+  <si>
+    <t>BIOFAC_479</t>
+  </si>
+  <si>
+    <t>BIOFAC_480</t>
+  </si>
+  <si>
+    <t>BIOFAC_481</t>
+  </si>
+  <si>
+    <t>BIOFAC_482</t>
+  </si>
+  <si>
+    <t>BIOFAC_483</t>
+  </si>
+  <si>
+    <t>BIOFAC_484</t>
+  </si>
+  <si>
+    <t>BIOFAC_485</t>
+  </si>
+  <si>
+    <t>BIOFAC_486</t>
+  </si>
+  <si>
+    <t>BIOFAC_487</t>
+  </si>
+  <si>
+    <t>BIOFAC_488</t>
+  </si>
+  <si>
+    <t>BIOFAC_489</t>
+  </si>
+  <si>
+    <t>BIOFAC_490</t>
+  </si>
+  <si>
+    <t>BIOFAC_491</t>
+  </si>
+  <si>
+    <t>BIOFAC_492</t>
+  </si>
+  <si>
+    <t>BIOFAC_493</t>
+  </si>
+  <si>
+    <t>BIOFAC_494</t>
+  </si>
+  <si>
+    <t>BIOFAC_495</t>
+  </si>
+  <si>
+    <t>BIOFAC_496</t>
+  </si>
+  <si>
+    <t>BIOFAC_497</t>
+  </si>
+  <si>
+    <t>BIOFAC_498</t>
+  </si>
+  <si>
+    <t>BIOFAC_499</t>
+  </si>
+  <si>
+    <t>BIOFAC_500</t>
+  </si>
+  <si>
+    <t>BIOFAC_501</t>
+  </si>
+  <si>
+    <t>BIOFAC_502</t>
+  </si>
+  <si>
+    <t>BIOFAC_503</t>
+  </si>
+  <si>
+    <t>BIOFAC_504</t>
+  </si>
+  <si>
+    <t>BIOFAC_505</t>
+  </si>
+  <si>
+    <t>BIOFAC_506</t>
+  </si>
+  <si>
+    <t>BIOFAC_507</t>
+  </si>
+  <si>
+    <t>BIOFAC_508</t>
+  </si>
+  <si>
+    <t>BIOFAC_509</t>
+  </si>
+  <si>
+    <t>BIOFAC_510</t>
+  </si>
+  <si>
+    <t>BIOFAC_511</t>
+  </si>
+  <si>
+    <t>BIOFAC_512</t>
+  </si>
+  <si>
+    <t>BIOFAC_513</t>
+  </si>
+  <si>
+    <t>BIOFAC_514</t>
+  </si>
+  <si>
+    <t>BIOFAC_515</t>
+  </si>
+  <si>
+    <t>BIOFAC_516</t>
+  </si>
+  <si>
+    <t>BIOFAC_517</t>
+  </si>
+  <si>
+    <t>BIOFAC_518</t>
+  </si>
+  <si>
+    <t>BIOFAC_519</t>
+  </si>
+  <si>
+    <t>BIOFAC_520</t>
+  </si>
+  <si>
+    <t>BIOFAC_521</t>
+  </si>
+  <si>
+    <t>BIOFAC_522</t>
+  </si>
+  <si>
+    <t>BIOFAC_523</t>
+  </si>
+  <si>
+    <t>BIOFAC_524</t>
+  </si>
+  <si>
+    <t>BIOFAC_525</t>
+  </si>
+  <si>
+    <t>BIOFAC_526</t>
+  </si>
+  <si>
+    <t>BIOFAC_527</t>
+  </si>
+  <si>
+    <t>BIOFAC_528</t>
+  </si>
+  <si>
+    <t>BIOFAC_529</t>
+  </si>
+  <si>
+    <t>BIOFAC_530</t>
+  </si>
+  <si>
+    <t>BIOFAC_531</t>
+  </si>
+  <si>
+    <t>BIOFAC_532</t>
+  </si>
+  <si>
+    <t>BIOFAC_533</t>
+  </si>
+  <si>
+    <t>BIOFAC_534</t>
+  </si>
+  <si>
+    <t>BIOFAC_535</t>
+  </si>
+  <si>
+    <t>BIOFAC_536</t>
+  </si>
+  <si>
+    <t>BIOFAC_537</t>
+  </si>
+  <si>
+    <t>BIOFAC_538</t>
+  </si>
+  <si>
+    <t>BIOFAC_539</t>
+  </si>
+  <si>
+    <t>BIOFAC_540</t>
+  </si>
+  <si>
+    <t>BIOFAC_541</t>
+  </si>
+  <si>
+    <t>BIOFAC_542</t>
+  </si>
+  <si>
+    <t>BIOFAC_543</t>
+  </si>
+  <si>
+    <t>BIOFAC_544</t>
+  </si>
+  <si>
+    <t>BIOFAC_545</t>
+  </si>
+  <si>
+    <t>BIOFAC_546</t>
+  </si>
+  <si>
+    <t>BIOFAC_547</t>
+  </si>
+  <si>
+    <t>BIOFAC_548</t>
+  </si>
+  <si>
+    <t>BIOFAC_549</t>
+  </si>
+  <si>
+    <t>BIOFAC_550</t>
+  </si>
+  <si>
+    <t>BIOFAC_551</t>
+  </si>
+  <si>
+    <t>BIOFAC_552</t>
+  </si>
+  <si>
+    <t>BIOFAC_553</t>
+  </si>
+  <si>
+    <t>BIOFAC_554</t>
+  </si>
+  <si>
+    <t>BIOFAC_555</t>
+  </si>
+  <si>
+    <t>BIOFAC_556</t>
+  </si>
+  <si>
+    <t>BIOFAC_557</t>
+  </si>
+  <si>
+    <t>BIOFAC_558</t>
+  </si>
+  <si>
+    <t>BIOFAC_559</t>
+  </si>
+  <si>
+    <t>BIOFAC_560</t>
+  </si>
+  <si>
+    <t>BIOFAC_561</t>
+  </si>
+  <si>
+    <t>BIOFAC_562</t>
+  </si>
+  <si>
+    <t>BIOFAC_563</t>
+  </si>
+  <si>
+    <t>BIOFAC_564</t>
+  </si>
+  <si>
+    <t>BIOFAC_565</t>
+  </si>
+  <si>
+    <t>BIOFAC_566</t>
+  </si>
+  <si>
+    <t>BIOFAC_567</t>
   </si>
 </sst>
 </file>
@@ -1851,6 +2305,816 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DF34553-FC16-4C39-B9D7-D6998E16C3C1}">
+  <dimension ref="A1:B100"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>578</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7984AFD9-7A75-40DA-A3D5-69022F0C5A2B}">
   <dimension ref="A1:C27"/>
@@ -5405,7 +6669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DF34553-FC16-4C39-B9D7-D6998E16C3C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C54EFDEA-5463-476B-8D31-193CF334D08B}">
   <dimension ref="A1:B67"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5429,51 +6693,81 @@
       <c r="A3">
         <v>2</v>
       </c>
+      <c r="B3" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
+      <c r="B4" t="s">
+        <v>429</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
+      <c r="B5" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
+      <c r="B6" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
+      <c r="B7" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
+      <c r="B8" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
+      <c r="B9" t="s">
+        <v>434</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
+      <c r="B10" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
+      <c r="B11" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
+      <c r="B12" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
@@ -5487,51 +6781,81 @@
       <c r="A14">
         <v>13</v>
       </c>
+      <c r="B14" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
+      <c r="B15" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
+      <c r="B16" t="s">
+        <v>440</v>
+      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
+      <c r="B17" t="s">
+        <v>441</v>
+      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
+      <c r="B18" t="s">
+        <v>442</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
+      <c r="B19" t="s">
+        <v>443</v>
+      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
+      <c r="B20" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
+      <c r="B21" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
+      <c r="B22" t="s">
+        <v>446</v>
+      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
+      <c r="B23" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
@@ -5545,51 +6869,81 @@
       <c r="A25">
         <v>24</v>
       </c>
+      <c r="B25" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
+      <c r="B26" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
+      <c r="B27" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
+      <c r="B28" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
+      <c r="B29" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
+      <c r="B30" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
+      <c r="B31" t="s">
+        <v>454</v>
+      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
+      <c r="B32" t="s">
+        <v>455</v>
+      </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
+      <c r="B33" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
+      <c r="B34" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
@@ -5603,51 +6957,81 @@
       <c r="A36">
         <v>35</v>
       </c>
+      <c r="B36" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
+      <c r="B37" t="s">
+        <v>459</v>
+      </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
+      <c r="B38" t="s">
+        <v>460</v>
+      </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
+      <c r="B39" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
+      <c r="B40" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
+      <c r="B41" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
+      <c r="B42" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
+      <c r="B43" t="s">
+        <v>465</v>
+      </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
+      <c r="B44" t="s">
+        <v>466</v>
+      </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
+      <c r="B45" t="s">
+        <v>467</v>
+      </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
@@ -5661,51 +7045,81 @@
       <c r="A47">
         <v>46</v>
       </c>
+      <c r="B47" t="s">
+        <v>468</v>
+      </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
+      <c r="B48" t="s">
+        <v>469</v>
+      </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
+      <c r="B49" t="s">
+        <v>470</v>
+      </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
+      <c r="B50" t="s">
+        <v>471</v>
+      </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
+      <c r="B51" t="s">
+        <v>472</v>
+      </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
+      <c r="B52" t="s">
+        <v>473</v>
+      </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
+      <c r="B53" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
+      <c r="B54" t="s">
+        <v>475</v>
+      </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
+      <c r="B55" t="s">
+        <v>476</v>
+      </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
+      <c r="B56" t="s">
+        <v>477</v>
+      </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
@@ -5719,50 +7133,80 @@
       <c r="A58">
         <v>57</v>
       </c>
+      <c r="B58" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
+      <c r="B59" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
+      <c r="B60" t="s">
+        <v>480</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
+      <c r="B61" t="s">
+        <v>481</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
+      <c r="B62" t="s">
+        <v>482</v>
+      </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
+      <c r="B63" t="s">
+        <v>483</v>
+      </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>487</v>
       </c>
     </row>
   </sheetData>
